--- a/stories/arbres/ATOM-TMP.SEM.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hanaé s'assoit sur son lit avec papa. Papa a un calendrier. Il montre sept cases. Papa dit : il y a sept jours dans l'ordre. Hanaé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau. Papa dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Hanaé répète les sept jours dans l'ordre. Le lendemain, à la cuisine, papa prépare le pain. Hanaé se souvient. Elle dit encore : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Même leçon, autre pièce. Les sept jours dans l'ordre commencent lundi. Ils finissent dimanche.</t>
+          <t>Hanaé s'assoit sur son lit avec papa. Papa a un calendrier. Il montre sept cases. Il y a sept jours dans l'ordre. Hanaé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Hanaé répète les sept jours dans l'ordre. Le lendemain, à la cuisine, papa prépare le pain. Hanaé se souvient. Elle dit encore : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Même leçon, autre pièce. Les sept jours dans l'ordre commencent lundi. Ils finissent dimanche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hanaé s'assoit sur son lit avec papa. Papa a un calendrier. Il montre sept cases.
+papa|Il y a sept jours dans l'ordre.
+narrateur|Hanaé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau.
+papa|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.
+narrateur|Hanaé répète les sept jours dans l'ordre. Le lendemain, à la cuisine, papa prépare le pain. Hanaé se souvient. Elle dit encore : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Même leçon, autre pièce. Les sept jours dans l'ordre commencent lundi. Ils finissent dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Après lundi, quel jour vient ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hanaé a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine. Plus tard, pareil.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hanaé pose un jeton sur mardi. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Hanaé répète les sept jours dans l'ordre. Le lendemain, à la cuisine, papa prépare le pain. Hanaé se souvient. Elle dit encore : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Même leçon, autre pièce. Les sept jours dans l'ordre commencent lundi. Ils finissent dimanche.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Après lundi, quel jour vient ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Hanaé a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine. Plus tard, pareil.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1843,7 @@
           <t>narrateur|Hanaé pose un jeton sur mardi. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hanaé dit les sept jours</t>
+          <t>Le ballon du square</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut un ballon rouge. Samedi au marché, le monsieur du ballon n'est pas là. Un écriteau dit dimanche, au square. Dimanche, le ballon s'envole un peu, puis tient.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hanaé s'assoit sur son lit avec papa. Papa a un calendrier. Il montre sept cases. Il y a sept jours dans l'ordre. Hanaé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Hanaé répète les sept jours dans l'ordre. Le lendemain, à la cuisine, papa prépare le pain. Hanaé se souvient. Elle dit encore : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Même leçon, autre pièce. Les sept jours dans l'ordre commencent lundi. Ils finissent dimanche.</t>
+          <t>Un chariot de paille grince sur les pavés. L'air sent l'oignon et le sucre chaud. Une caisse d'oranges brille au soleil bas. Papa tient un sac de toile rêche. Tu as senti l'oignon, Mila ? Il pique un peu. C'est samedi. C'est le jour du marché. En ce moment, Mila cherche un fil rouge. Je veux un ballon. Un ballon rouge. On le cherche. Ils passent entre les caisses. Un poulet rôti fume tout près. Mila lève les yeux. Pas de fil. Pas de ballon. Il n'est pas là. Le monsieur du ballon n'est pas au marché. Un écriteau jaune penche contre une caisse. Mila s'approche. Il y a un dessin de ballon. Dimanche, au square. C'est écrit. Pas ce samedi ? Ce samedi, c'est le marché. Demain, c'est dimanche. La semaine a sept jours. Mila serre le bord du sac. Le tissu râpe sa paume. On prend des oignons alors. Oui. Et demain, le square. Papa glisse deux oignons dans le sac. Ils sont secs, un peu bruns. Le ballon m'attend ? Au square, demain. Quel jour vient après samedi ? Dimanche. Oui. Le chariot de paille grince encore, plus loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hanaé s'assoit sur son lit avec papa. Papa a un calendrier. Il montre &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; cases. Papa dit : il y a sept jours dans l'ordre. Hanaé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau. Papa dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Hanaé répète les sept jours dans l'ordre. Le lendemain, à la cuisine, papa prépare le pain. Hanaé se souvient. Elle dit encore : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Même leçon, autre pièce. Les sept jours dans l'ordre commencent lundi. Ils finissent dimanche.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un chariot de paille grince sur les pavés. L'air sent l'oignon et le sucre chaud. Une caisse d'oranges brille au soleil bas. Papa tient un sac de toile rêche. Tu as senti l'oignon, Mila ? Il pique un peu. C'est samedi. C'est le jour du marché. En ce moment, Mila cherche un fil rouge. Je veux un ballon. Un ballon rouge. On le cherche. Ils passent entre les caisses. Un poulet rôti fume tout près. Mila lève les yeux. Pas de fil. Pas de ballon. Il n'est pas là. Le monsieur du ballon n'est pas au marché. Un écriteau jaune penche contre une caisse. Mila s'approche. Il y a un dessin de ballon. Dimanche, au square. C'est écrit. Pas ce samedi ? Ce samedi, c'est le marché. Demain, c'est dimanche. La semaine a sept jours. Mila serre le bord du sac. Le tissu râpe sa paume. On prend des oignons alors. Oui. Et demain, le square. Papa glisse deux oignons dans le sac. Ils sont secs, un peu bruns. Le ballon m'attend ? Au square, demain. Quel jour vient après samedi ? Dimanche. Oui. Le chariot de paille grince encore, plus loin.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,47 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hanaé s'assoit sur son lit avec papa. Papa a un calendrier. Il montre sept cases.
-papa|Il y a sept jours dans l'ordre.
-narrateur|Hanaé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau.
-papa|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.
-narrateur|Hanaé répète les sept jours dans l'ordre. Le lendemain, à la cuisine, papa prépare le pain. Hanaé se souvient. Elle dit encore : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Même leçon, autre pièce. Les sept jours dans l'ordre commencent lundi. Ils finissent dimanche.</t>
+          <t>narrateur|Un chariot de paille grince sur les pavés.
+narrateur|L'air sent l'oignon et le sucre chaud.
+narrateur|Une caisse d'oranges brille au soleil bas.
+narrateur|Papa tient un sac de toile rêche.
+papa|Tu as senti l'oignon, Mila ?
+enfant-f|Il pique un peu.
+papa|C'est samedi.
+papa|C'est le jour du marché.
+narrateur|En ce moment, Mila cherche un fil rouge.
+enfant-f|Je veux un ballon.
+enfant-f|Un ballon rouge.
+papa|On le cherche.
+narrateur|Ils passent entre les caisses.
+narrateur|Un poulet rôti fume tout près.
+narrateur|Mila lève les yeux.
+narrateur|Pas de fil.
+narrateur|Pas de ballon.
+enfant-f|Il n'est pas là.
+papa|Le monsieur du ballon n'est pas au marché.
+narrateur|Un écriteau jaune penche contre une caisse.
+narrateur|Mila s'approche.
+enfant-f|Il y a un dessin de ballon.
+papa|Dimanche, au square.
+papa|C'est écrit.
+enfant-f|Pas ce samedi ?
+papa|Ce samedi, c'est le marché.
+papa|Demain, c'est dimanche.
+papa|La semaine a sept jours.
+narrateur|Mila serre le bord du sac.
+narrateur|Le tissu râpe sa paume.
+enfant-f|On prend des oignons alors.
+papa|Oui.
+papa|Et demain, le square.
+narrateur|Papa glisse deux oignons dans le sac.
+narrateur|Ils sont secs, un peu bruns.
+enfant-f|Le ballon m'attend ?
+papa|Au square, demain.
+papa|Quel jour vient après samedi ?
+enfant-f|Dimanche.
+papa|Oui.
+narrateur|Le chariot de paille grince encore, plus loin.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,27 +1396,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Après samedi, quel jour vient ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Après samedi, quel jour vient ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Après lundi, quel jour vient ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après lundi, quel jour vient ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Après lundi, quel jour vient ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>mardi</t>
+          <t>dimanche</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>mardi | c'est mardi | le mardi</t>
+          <t>dimanche | le dimanche | c'est dimanche</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1431,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Lundi, puis mardi. Quel jour après lundi ?</t>
+          <t>Samedi, le marché. Quel jour vient après ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1425,14 +1473,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1552,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Après lundi, quel jour vient ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Après samedi, quel jour vient ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1579,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hanaé a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine. Plus tard, pareil.</t>
+          <t>Le square sent l'herbe coupée. Un manège tourne tout doux, sans musique forte. C'est dimanche, Mila. Le bon jour du square. Le monsieur ! Un homme tient un bouquet de ballons. Le rouge est au milieu, un peu plus petit. Mila tend les deux mains. Tu le tiens bien ? Oui. Le fil est lisse, un peu collant. Le ballon tire vers le ciel. Il veut partir. On fait un nœud au poignet. Papa noue le fil tout doux. Le ballon reste, il danse. Il est à moi. Merci, Mila. Tu as attendu dimanche. Un oignon du sac sent encore, dans le fond.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hanaé a dit les &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; jours dans l'ordre. Lundi commence. Dimanche termine. Plus tard, pareil.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le square sent l'herbe coupée. Un manège tourne tout doux, sans musique forte. C'est dimanche, Mila. Le bon jour du square. Le monsieur ! Un homme tient un bouquet de ballons. Le rouge est au milieu, un peu plus petit. Mila tend les deux mains. Tu le tiens bien ? Oui. Le fil est lisse, un peu collant. Le ballon tire vers le ciel. Il veut partir. On fait un nœud au poignet. Papa noue le fil tout doux. Le ballon reste, il danse. Il est à moi. Merci, Mila. Tu as attendu dimanche. Un oignon du sac sent encore, dans le fond.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1600,7 +1647,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,10 +1723,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hanaé a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine. Plus tard, pareil.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le square sent l'herbe coupée.
+narrateur|Un manège tourne tout doux, sans musique forte.
+papa|C'est dimanche, Mila.
+papa|Le bon jour du square.
+enfant-f|Le monsieur !
+narrateur|Un homme tient un bouquet de ballons.
+narrateur|Le rouge est au milieu, un peu plus petit.
+narrateur|Mila tend les deux mains.
+papa|Tu le tiens bien ?
+enfant-f|Oui.
+narrateur|Le fil est lisse, un peu collant.
+narrateur|Le ballon tire vers le ciel.
+enfant-f|Il veut partir.
+papa|On fait un nœud au poignet.
+narrateur|Papa noue le fil tout doux.
+narrateur|Le ballon reste, il danse.
+enfant-f|Il est à moi.
+papa|Merci, Mila.
+papa|Tu as attendu dimanche.
+narrateur|Un oignon du sac sent encore, dans le fond.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hanaé pose un jeton sur mardi. Papa sourit.</t>
+          <t>Ils s'assoient sur le banc du square. Le bois est tiède. Samedi, le marché. Dimanche, le square. Et le ballon. Oui. Le ballon tape l'épaule de Mila. Toc, tout léger. Il est rouge comme l'orange. Presque. Un pigeon picore une miette. Mila tient le fil plus fort. On rentre ? Le ballon vient. Oui. Le manège s'arrête un moment. Le square redevient calme. Demain, c'est lundi. Oui. Le ballon reste avec nous.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hanaé pose un jeton sur mardi. Papa sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils s'assoient sur le banc du square. Le bois est tiède. Samedi, le marché. Dimanche, le square. Et le ballon. Oui. Le ballon tape l'épaule de Mila. Toc, tout léger. Il est rouge comme l'orange. Presque. Un pigeon picore une miette. Mila tient le fil plus fort. On rentre ? Le ballon vient. Oui. Le manège s'arrête un moment. Le square redevient calme. Demain, c'est lundi. Oui. Le ballon reste avec nous.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1772,7 +1837,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1840,10 +1905,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hanaé pose un jeton sur mardi. Papa sourit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils s'assoient sur le banc du square.
+narrateur|Le bois est tiède.
+papa|Samedi, le marché.
+papa|Dimanche, le square.
+enfant-f|Et le ballon.
+papa|Oui.
+narrateur|Le ballon tape l'épaule de Mila.
+narrateur|Toc, tout léger.
+enfant-f|Il est rouge comme l'orange.
+papa|Presque.
+narrateur|Un pigeon picore une miette.
+narrateur|Mila tient le fil plus fort.
+papa|On rentre ?
+enfant-f|Le ballon vient.
+papa|Oui.
+narrateur|Le manège s'arrête un moment.
+narrateur|Le square redevient calme.
+enfant-f|Demain, c'est lundi.
+papa|Oui.
+papa|Le ballon reste avec nous.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ballon rouge frotte le linteau de la porte. Il est rentré. Oui. Samedi le marché, dimanche le square. Le fil fait une ombre mince sur le carrelage.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ballon rouge frotte le linteau de la porte. Il est rentré. Oui. Samedi le marché, dimanche le square. Le fil fait une ombre mince sur le carrelage.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1936,7 +2019,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2008,10 +2091,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le ballon rouge frotte le linteau de la porte.
+enfant-f|Il est rentré.
+papa|Oui.
+papa|Samedi le marché, dimanche le square.
+narrateur|Le fil fait une ombre mince sur le carrelage.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre puis cuisine</t>
+          <t>marché du samedi, puis square du dimanche</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hanaé, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
